--- a/Ejemplo1 Bayes.xlsx
+++ b/Ejemplo1 Bayes.xlsx
@@ -8,7 +8,8 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Marketing digital" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="detector enfermedad" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,18 +21,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t xml:space="preserve">B: Ver juegos de PC</t>
   </si>
   <si>
-    <t xml:space="preserve">X</t>
+    <t xml:space="preserve">X (mulktipl)</t>
   </si>
   <si>
     <t xml:space="preserve">P(A / B) = P(A ∩ B) / P(B)</t>
   </si>
   <si>
     <t xml:space="preserve">Nuevos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Encuestas</t>
   </si>
   <si>
     <t xml:space="preserve">Despejando:</t>
@@ -102,6 +106,9 @@
     <t xml:space="preserve">Ocasion</t>
   </si>
   <si>
+    <t xml:space="preserve">:)</t>
+  </si>
+  <si>
     <t xml:space="preserve">P(A₂) = 0.3</t>
   </si>
   <si>
@@ -195,6 +202,80 @@
   </si>
   <si>
     <t xml:space="preserve">P(B) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positivo/Enfermo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P(Enfermo ∩ +)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enfermo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-/Enfermo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Falsos positivos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positivo /Sano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P(Sano y +)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-/Sano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P(+)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P(E/+)=</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">P(E </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">∩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> +) / </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">P(+)=</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -205,7 +286,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="14">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -234,6 +315,12 @@
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FF81D41A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF00A933"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -241,6 +328,13 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF81D41A"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -267,6 +361,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -274,6 +374,12 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF81D41A"/>
+        <bgColor rgb="FF969696"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -301,12 +407,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF81D41A"/>
-        <bgColor rgb="FF969696"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFE0C2CD"/>
         <bgColor rgb="FFFFD8CE"/>
       </patternFill>
@@ -346,7 +446,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -359,44 +459,60 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -469,6 +585,380 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>100080</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>121680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>600840</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>57960</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="0" name="Línea 1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="912960" y="446760"/>
+          <a:ext cx="500760" cy="261360"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>135360</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>81000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>32760</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>80280</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="Línea 2"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="948240" y="731160"/>
+          <a:ext cx="671400" cy="324360"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>105840</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>92520</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>56520</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>33840</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Línea 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="918720" y="742680"/>
+          <a:ext cx="724680" cy="1280160"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>653760</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>5760</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>64080</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>156240</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="Línea 4"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="1466640" y="330840"/>
+          <a:ext cx="471240" cy="150480"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>683280</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>121680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>40320</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>149760</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Línea 5"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1496160" y="446760"/>
+          <a:ext cx="417960" cy="353160"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>23400</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>144720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>95760</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>5040</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Línea 6"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="1610280" y="1119960"/>
+          <a:ext cx="359280" cy="23040"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>35280</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>17280</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>19440</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>138240</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Línea 7"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1622160" y="1155240"/>
+          <a:ext cx="271080" cy="446040"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>76680</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>29160</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>207720</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>121680</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Línea 8"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1663560" y="2018160"/>
+          <a:ext cx="417960" cy="92520"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>94320</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>75600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>66600</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>86040</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="Línea 9"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1681200" y="2064600"/>
+          <a:ext cx="259200" cy="497880"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -613,141 +1103,148 @@
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="3"/>
       <c r="L2" s="0" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="3" t="s">
-        <v>5</v>
+      <c r="B3" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>0.6</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>6</v>
+      <c r="D3" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>0.05</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G3" s="6" t="n">
         <f aca="false">C3*E3</f>
         <v>0.03</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" s="6"/>
+      <c r="I3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="8"/>
       <c r="L3" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="3"/>
-      <c r="D4" s="3"/>
+      <c r="B4" s="4"/>
+      <c r="D4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="3"/>
-      <c r="D5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I5" s="7" t="s">
+      <c r="B5" s="4"/>
+      <c r="D5" s="4" t="s">
         <v>11</v>
       </c>
+      <c r="I5" s="9" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="3"/>
-      <c r="D6" s="3"/>
+      <c r="B6" s="4"/>
+      <c r="D6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="3"/>
-      <c r="I7" s="0" t="n">
+      <c r="B7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="I7" s="10" t="n">
         <f aca="false">0.08 / 0.14</f>
         <v>0.571428571428571</v>
       </c>
+      <c r="J7" s="0" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="3" t="s">
-        <v>13</v>
+      <c r="B8" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>0.3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>14</v>
+      <c r="D8" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>0.1</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="G8" s="11" t="n">
         <f aca="false">C8*E8</f>
         <v>0.03</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="3"/>
-      <c r="D9" s="3"/>
+      <c r="B9" s="4"/>
+      <c r="D9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="3"/>
-      <c r="D10" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>17</v>
+      <c r="B10" s="4"/>
+      <c r="D10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="24.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="I11" s="10" t="s">
-        <v>18</v>
+      <c r="B11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="I11" s="13" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="3"/>
+      <c r="B12" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="3" t="s">
-        <v>20</v>
+      <c r="B13" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="D13" s="11" t="s">
-        <v>21</v>
+      <c r="D13" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>0.8</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G13" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="G13" s="14" t="n">
         <f aca="false">C13*E13</f>
         <v>0.08</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D15" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G15" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="4" t="n">
         <f aca="false">SUM(G3:G13)</f>
         <v>0.14</v>
       </c>
@@ -757,7 +1254,7 @@
       <c r="G16" s="0"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="3" t="n">
+      <c r="B20" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -772,5 +1269,119 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Página &amp;P</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B1:I15"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.67"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H1" s="0" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E2" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="H2" s="0" t="n">
+        <f aca="false">C4*G2</f>
+        <v>0.00099</v>
+      </c>
+      <c r="I2" s="0" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <f aca="false">1/1000</f>
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E5" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E9" s="0" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="0" t="n">
+        <f aca="false"> 1-C4</f>
+        <v>0.999</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H10" s="0" t="n">
+        <f aca="false">C10*G10</f>
+        <v>0.01998</v>
+      </c>
+      <c r="I10" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E12" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H14" s="15" t="n">
+        <f aca="false">H2+H10</f>
+        <v>0.02097</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="17.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C15" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <f aca="false">H2/H14</f>
+        <v>0.0472103004291845</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Página &amp;P</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>